--- a/output/pdf_financials_xlsx/CCMM.xlsx
+++ b/output/pdf_financials_xlsx/CCMM.xlsx
@@ -2103,10 +2103,10 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.0137</v>
+        <v>0.0295</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.0235</v>
+        <v>0.5065</v>
       </c>
     </row>
     <row r="93">
@@ -3238,7 +3238,11 @@
           <t>Warrants reserve (note 8)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CCMM.xlsx
+++ b/output/pdf_financials_xlsx/CCMM.xlsx
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.007757</v>
+        <v>1.07893</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.09780999999999999</v>
+        <v>1.611111</v>
       </c>
     </row>
     <row r="11">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.007757</v>
+        <v>-1.07893</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.09780999999999999</v>
+        <v>-1.611111</v>
       </c>
     </row>
     <row r="12">
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.012521</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.305783</v>
       </c>
     </row>
     <row r="35">
@@ -1079,10 +1079,10 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.012521</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.305783</v>
       </c>
     </row>
     <row r="37">
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.112679</v>
+        <v>0.100158</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.786483</v>
+        <v>0.4807</v>
       </c>
     </row>
     <row r="49">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">

--- a/output/pdf_financials_xlsx/CCMM.xlsx
+++ b/output/pdf_financials_xlsx/CCMM.xlsx
@@ -3839,7 +3839,11 @@
           <t>Cash, at beginning of the year</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
